--- a/artfynd/Gåstjärnen artfynd.xlsx
+++ b/artfynd/Gåstjärnen artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112436030</v>
+        <v>112187755</v>
       </c>
       <c r="B2" t="n">
-        <v>92551</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680149</v>
+        <v>680359</v>
       </c>
       <c r="R2" t="n">
-        <v>7102308</v>
+        <v>7102296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112436026</v>
+        <v>112187753</v>
       </c>
       <c r="B3" t="n">
-        <v>92539</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680093</v>
+        <v>680343</v>
       </c>
       <c r="R3" t="n">
-        <v>7102503</v>
+        <v>7102115</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112187754</v>
+        <v>112187762</v>
       </c>
       <c r="B4" t="n">
-        <v>92551</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680350</v>
+        <v>680260</v>
       </c>
       <c r="R4" t="n">
-        <v>7102140</v>
+        <v>7102404</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112187763</v>
+        <v>112187761</v>
       </c>
       <c r="B5" t="n">
-        <v>75075</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680291</v>
+        <v>680234</v>
       </c>
       <c r="R5" t="n">
-        <v>7102390</v>
+        <v>7102398</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,14 +1079,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112436029</v>
+        <v>112187751</v>
       </c>
       <c r="B6" t="n">
-        <v>92551</v>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680134</v>
+        <v>680386</v>
       </c>
       <c r="R6" t="n">
-        <v>7102426</v>
+        <v>7102054</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112187753</v>
+        <v>112187754</v>
       </c>
       <c r="B7" t="n">
-        <v>78647</v>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680343</v>
+        <v>680350</v>
       </c>
       <c r="R7" t="n">
-        <v>7102115</v>
+        <v>7102140</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112187756</v>
+        <v>112436025</v>
       </c>
       <c r="B8" t="n">
-        <v>92529</v>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680361</v>
+        <v>680102</v>
       </c>
       <c r="R8" t="n">
-        <v>7102367</v>
+        <v>7102515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112187750</v>
+        <v>112436029</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680389</v>
+        <v>680134</v>
       </c>
       <c r="R9" t="n">
-        <v>7102041</v>
+        <v>7102426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112436028</v>
+        <v>112436030</v>
       </c>
       <c r="B10" t="n">
-        <v>92529</v>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680118</v>
+        <v>680149</v>
       </c>
       <c r="R10" t="n">
-        <v>7102465</v>
+        <v>7102308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112187760</v>
+        <v>112187756</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680242</v>
+        <v>680361</v>
       </c>
       <c r="R11" t="n">
-        <v>7102081</v>
+        <v>7102367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112187761</v>
+        <v>112436028</v>
       </c>
       <c r="B12" t="n">
-        <v>82792</v>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680234</v>
+        <v>680118</v>
       </c>
       <c r="R12" t="n">
-        <v>7102398</v>
+        <v>7102465</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112187752</v>
+        <v>112187759</v>
       </c>
       <c r="B13" t="n">
-        <v>92563</v>
+        <v>93201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680386</v>
+        <v>680353</v>
       </c>
       <c r="R13" t="n">
-        <v>7102054</v>
+        <v>7102412</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,32 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112187751</v>
+        <v>112436026</v>
       </c>
       <c r="B14" t="n">
-        <v>92551</v>
+        <v>93201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680386</v>
+        <v>680093</v>
       </c>
       <c r="R14" t="n">
-        <v>7102054</v>
+        <v>7102503</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112187762</v>
+        <v>112187757</v>
       </c>
       <c r="B15" t="n">
-        <v>91245</v>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680260</v>
+        <v>680272</v>
       </c>
       <c r="R15" t="n">
-        <v>7102404</v>
+        <v>7102246</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,48 +2089,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16846926</v>
+        <v>112436027</v>
       </c>
       <c r="B16" t="n">
-        <v>91263</v>
+        <v>90691</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Holmtjärnen, Ång</t>
+          <t>Lång-Viskasjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680199</v>
+        <v>680108</v>
       </c>
       <c r="R16" t="n">
-        <v>7102032</v>
+        <v>7102496</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2013-06-15</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2013-06-15</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2170,26 +2170,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>gransumpskog</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2200,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112187759</v>
+        <v>112187750</v>
       </c>
       <c r="B17" t="n">
-        <v>92539</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680353</v>
+        <v>680389</v>
       </c>
       <c r="R17" t="n">
-        <v>7102412</v>
+        <v>7102041</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,32 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112436027</v>
+        <v>112187763</v>
       </c>
       <c r="B18" t="n">
-        <v>90001</v>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680108</v>
+        <v>680291</v>
       </c>
       <c r="R18" t="n">
-        <v>7102496</v>
+        <v>7102390</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,32 +2392,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112187757</v>
+        <v>112187760</v>
       </c>
       <c r="B19" t="n">
-        <v>92571</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680272</v>
+        <v>680242</v>
       </c>
       <c r="R19" t="n">
-        <v>7102246</v>
+        <v>7102081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2496,208 +2486,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>112436025</v>
-      </c>
-      <c r="B20" t="n">
-        <v>92551</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Lång-Viskasjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>680102</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7102515</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>112187755</v>
-      </c>
-      <c r="B21" t="n">
-        <v>96614</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>53</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Lång-Viskasjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>680359</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7102296</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
